--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_37.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1987701.780382948</v>
+        <v>1979809.26963715</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7069717.394383963</v>
+        <v>7467636.99034356</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7069717.394383963</v>
+        <v>7467636.99034356</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421524.090381441</v>
+        <v>1235436.710599796</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421524.090381441</v>
+        <v>1235436.710599796</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17700731.26043007</v>
+        <v>17765351.10692801</v>
       </c>
     </row>
   </sheetData>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>285.2549665268089</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>118.6979892794115</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -897,7 +897,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>28.67298744257963</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>210.6156651633976</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -979,13 +979,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>167.1158402638074</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1024,7 +1024,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>342.0664376127545</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1137,7 +1137,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>22.69712130959848</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>18.33383170272989</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>308.431151305653</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>78.52683295460992</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>262.4925055126944</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H12" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,28 +1492,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U12" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V12" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1523,25 +1523,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1550,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>45.14518808597779</v>
+        <v>232.0181330124256</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>269.8481678023229</v>
+        <v>247.2591591877369</v>
       </c>
       <c r="T14" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V14" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>418.8666685380672</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H15" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U15" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V15" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1769,16 +1769,16 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.3775199254117115</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>278.3114466390653</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1823,13 +1823,13 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1839,25 +1839,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H17" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>31.37179138541422</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>269.8481678023229</v>
+        <v>247.2591591877369</v>
       </c>
       <c r="T17" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V17" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H18" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,28 +1966,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S18" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U18" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V18" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2009,13 +2009,13 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>45.14518808597777</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>295.6316114025499</v>
+        <v>10.9107468745654</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2076,28 +2076,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>183.0096587035274</v>
+        <v>160.4206500889414</v>
       </c>
       <c r="I20" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,28 +2124,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T20" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U20" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V20" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H21" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,28 +2203,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U21" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V21" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2267,19 +2267,19 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>258.9489357531583</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>345.9207354288559</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2313,28 +2313,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I23" t="n">
-        <v>5.493192557119869</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,28 +2361,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T23" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U23" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V23" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="24">
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H24" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,28 +2440,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U24" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V24" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2474,22 +2474,22 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D25" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F25" t="n">
-        <v>49.38285596774193</v>
+        <v>1.272267689555869</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>168.3923726157678</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2534,13 +2534,13 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2720,13 +2720,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.9062680585641492</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>361.6755817285639</v>
+        <v>367.1687742856838</v>
       </c>
       <c r="U29" t="n">
         <v>424.2212965486107</v>
@@ -2945,16 +2945,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>50.44748169912842</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>280.2405814329721</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>233.3594533926489</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S32" t="n">
         <v>269.8481678023229</v>
@@ -3093,7 +3093,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>286.3174326828064</v>
+        <v>291.8106252399262</v>
       </c>
     </row>
     <row r="33">
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>345.9207354288559</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -3403,7 +3403,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>82.37314290982852</v>
+        <v>155.4146630973942</v>
       </c>
       <c r="X36" t="n">
         <v>69.86273944538755</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>82.37314290982852</v>
+        <v>145.050905435271</v>
       </c>
       <c r="X39" t="n">
         <v>69.86273944538755</v>
@@ -3744,7 +3744,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>58.32868099228319</v>
+        <v>54.36328960686865</v>
       </c>
       <c r="F41" t="n">
         <v>54.88962870801186</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3823,13 +3823,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3868,10 +3868,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U42" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
         <v>64.51066719152016</v>
@@ -4054,13 +4054,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>81.10557774904923</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4108,7 +4108,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V45" t="n">
         <v>64.51066719152016</v>
@@ -4324,13 +4324,13 @@
         <v>33.68</v>
       </c>
       <c r="K2" t="n">
-        <v>33.68</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>33.68</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>433.6300000000001</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>850.4200000000001</v>
@@ -4339,7 +4339,7 @@
         <v>1267.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="Q2" t="n">
         <v>1684</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>496.6438703204933</v>
+        <v>321.8163298250595</v>
       </c>
       <c r="C3" t="n">
-        <v>496.6438703204933</v>
+        <v>321.8163298250595</v>
       </c>
       <c r="D3" t="n">
-        <v>496.6438703204933</v>
+        <v>321.8163298250595</v>
       </c>
       <c r="E3" t="n">
-        <v>496.6438703204933</v>
+        <v>33.68</v>
       </c>
       <c r="F3" t="n">
-        <v>153.5769588680924</v>
+        <v>33.68</v>
       </c>
       <c r="G3" t="n">
-        <v>153.5769588680924</v>
+        <v>33.68</v>
       </c>
       <c r="H3" t="n">
-        <v>153.5769588680924</v>
+        <v>33.68</v>
       </c>
       <c r="I3" t="n">
         <v>33.68</v>
@@ -4421,31 +4421,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S3" t="n">
-        <v>973.1146453614743</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T3" t="n">
-        <v>967.7027613033796</v>
+        <v>792.8752208079458</v>
       </c>
       <c r="U3" t="n">
-        <v>967.4902766971303</v>
+        <v>792.6627362016965</v>
       </c>
       <c r="V3" t="n">
-        <v>952.8330371097362</v>
+        <v>778.0054966143024</v>
       </c>
       <c r="W3" t="n">
-        <v>920.1328927563741</v>
+        <v>745.3053522609403</v>
       </c>
       <c r="X3" t="n">
-        <v>900.0695195792149</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="Y3" t="n">
-        <v>496.6438703204933</v>
+        <v>321.8163298250595</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>704.3785197772106</v>
+        <v>617.0186027233684</v>
       </c>
       <c r="C4" t="n">
-        <v>704.3785197772106</v>
+        <v>743.0206085418042</v>
       </c>
       <c r="D4" t="n">
-        <v>704.3785197772106</v>
+        <v>856.3397526668043</v>
       </c>
       <c r="E4" t="n">
-        <v>822.2074239886236</v>
+        <v>974.1686568782173</v>
       </c>
       <c r="F4" t="n">
-        <v>946.5683965805591</v>
+        <v>1098.529629470153</v>
       </c>
       <c r="G4" t="n">
-        <v>946.5683965805591</v>
+        <v>1251.936195357038</v>
       </c>
       <c r="H4" t="n">
-        <v>1116.084981739957</v>
+        <v>1251.936195357038</v>
       </c>
       <c r="I4" t="n">
-        <v>1183.403502424373</v>
+        <v>1473.069074293121</v>
       </c>
       <c r="J4" t="n">
         <v>1544.487243076824</v>
@@ -4509,22 +4509,22 @@
         <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>259.005934252978</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>505.5571268912646</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V4" t="n">
-        <v>704.3785197772106</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="W4" t="n">
-        <v>704.3785197772106</v>
+        <v>242.8211733538506</v>
       </c>
       <c r="X4" t="n">
-        <v>704.3785197772106</v>
+        <v>393.851964378044</v>
       </c>
       <c r="Y4" t="n">
-        <v>704.3785197772106</v>
+        <v>505.2612650570763</v>
       </c>
     </row>
     <row r="5">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>285.4463380542246</v>
+        <v>266.9273161322752</v>
       </c>
       <c r="C5" t="n">
-        <v>235.472016596655</v>
+        <v>216.9529946747056</v>
       </c>
       <c r="D5" t="n">
         <v>206.5094030182917</v>
@@ -4561,22 +4561,22 @@
         <v>33.68</v>
       </c>
       <c r="K5" t="n">
-        <v>450.47</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>867.26</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="M5" t="n">
+        <v>850.4200000000001</v>
+      </c>
+      <c r="N5" t="n">
         <v>1267.21</v>
       </c>
-      <c r="N5" t="n">
-        <v>1684</v>
-      </c>
       <c r="O5" t="n">
-        <v>1684</v>
+        <v>1267.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1684</v>
+        <v>1267.21</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
@@ -4600,10 +4600,10 @@
         <v>674.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>480.7157780929932</v>
+        <v>462.1967561710438</v>
       </c>
       <c r="Y5" t="n">
-        <v>368.2739268982392</v>
+        <v>349.7549049762899</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>900.0695195792149</v>
+        <v>385.1322089875785</v>
       </c>
       <c r="C6" t="n">
-        <v>900.0695195792149</v>
+        <v>385.1322089875785</v>
       </c>
       <c r="D6" t="n">
-        <v>548.6173105916364</v>
+        <v>33.68</v>
       </c>
       <c r="E6" t="n">
-        <v>202.4838790543509</v>
+        <v>33.68</v>
       </c>
       <c r="F6" t="n">
-        <v>202.4838790543509</v>
+        <v>33.68</v>
       </c>
       <c r="G6" t="n">
         <v>33.68</v>
@@ -4658,31 +4658,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S6" t="n">
-        <v>973.1146453614743</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T6" t="n">
-        <v>967.7027613033796</v>
+        <v>452.765450711743</v>
       </c>
       <c r="U6" t="n">
-        <v>967.4902766971303</v>
+        <v>452.5529661054938</v>
       </c>
       <c r="V6" t="n">
-        <v>952.8330371097362</v>
+        <v>437.8957265180997</v>
       </c>
       <c r="W6" t="n">
-        <v>920.1328927563741</v>
+        <v>405.1955821647376</v>
       </c>
       <c r="X6" t="n">
-        <v>900.0695195792149</v>
+        <v>385.1322089875785</v>
       </c>
       <c r="Y6" t="n">
-        <v>900.0695195792149</v>
+        <v>385.1322089875785</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>408.5557524108052</v>
+        <v>643.949077349637</v>
       </c>
       <c r="C7" t="n">
-        <v>534.557758229241</v>
+        <v>643.949077349637</v>
       </c>
       <c r="D7" t="n">
-        <v>647.8769023542411</v>
+        <v>757.2682214746371</v>
       </c>
       <c r="E7" t="n">
-        <v>765.7058065656541</v>
+        <v>792.7540383288922</v>
       </c>
       <c r="F7" t="n">
-        <v>890.0667791575896</v>
+        <v>792.7540383288922</v>
       </c>
       <c r="G7" t="n">
-        <v>1043.473345044475</v>
+        <v>792.7540383288922</v>
       </c>
       <c r="H7" t="n">
-        <v>1212.989930203873</v>
+        <v>962.2706234882897</v>
       </c>
       <c r="I7" t="n">
-        <v>1434.122809139956</v>
+        <v>1183.403502424373</v>
       </c>
       <c r="J7" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K7" t="n">
         <v>1544.487243076824</v>
@@ -4743,25 +4743,25 @@
         <v>33.68</v>
       </c>
       <c r="S7" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U7" t="n">
-        <v>125.2555334720955</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V7" t="n">
-        <v>125.2555334720955</v>
+        <v>269.7516479801191</v>
       </c>
       <c r="W7" t="n">
-        <v>297.146451731773</v>
+        <v>269.7516479801191</v>
       </c>
       <c r="X7" t="n">
-        <v>297.146451731773</v>
+        <v>420.7824390043126</v>
       </c>
       <c r="Y7" t="n">
-        <v>408.5557524108052</v>
+        <v>532.1917396833448</v>
       </c>
     </row>
     <row r="8">
@@ -4771,13 +4771,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>285.4463380542246</v>
+        <v>266.9273161322752</v>
       </c>
       <c r="C8" t="n">
-        <v>235.472016596655</v>
+        <v>216.9529946747056</v>
       </c>
       <c r="D8" t="n">
-        <v>225.028424940241</v>
+        <v>206.5094030182917</v>
       </c>
       <c r="E8" t="n">
         <v>202.1020397790304</v>
@@ -4804,13 +4804,13 @@
         <v>424.9891130376557</v>
       </c>
       <c r="M8" t="n">
-        <v>424.9891130376558</v>
+        <v>841.7791130376559</v>
       </c>
       <c r="N8" t="n">
-        <v>841.7791130376559</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="O8" t="n">
-        <v>1258.569113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="P8" t="n">
         <v>1267.21</v>
@@ -4819,28 +4819,28 @@
         <v>1684</v>
       </c>
       <c r="R8" t="n">
-        <v>1684</v>
+        <v>1665.480978078051</v>
       </c>
       <c r="S8" t="n">
-        <v>1588.193769896644</v>
+        <v>1569.674747974694</v>
       </c>
       <c r="T8" t="n">
-        <v>1399.632576231427</v>
+        <v>1381.113554309478</v>
       </c>
       <c r="U8" t="n">
-        <v>1147.893892848992</v>
+        <v>1129.374870927043</v>
       </c>
       <c r="V8" t="n">
-        <v>915.7211411653319</v>
+        <v>897.2021192433824</v>
       </c>
       <c r="W8" t="n">
-        <v>674.9398522956878</v>
+        <v>656.4208303737385</v>
       </c>
       <c r="X8" t="n">
-        <v>480.7157780929932</v>
+        <v>462.1967561710438</v>
       </c>
       <c r="Y8" t="n">
-        <v>368.2739268982392</v>
+        <v>349.7549049762899</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C9" t="n">
-        <v>33.68</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="D9" t="n">
-        <v>33.68</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="E9" t="n">
-        <v>33.68</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="F9" t="n">
-        <v>33.68</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="G9" t="n">
-        <v>33.68</v>
+        <v>588.5229020987573</v>
       </c>
       <c r="H9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="I9" t="n">
         <v>33.68</v>
@@ -4904,22 +4904,22 @@
         <v>973.1146453614743</v>
       </c>
       <c r="T9" t="n">
-        <v>893.7946120739896</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>893.5821274677403</v>
+        <v>967.4902766971303</v>
       </c>
       <c r="V9" t="n">
-        <v>878.9248878803462</v>
+        <v>952.8330371097362</v>
       </c>
       <c r="W9" t="n">
-        <v>846.2247435269841</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>422.1209663094209</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="Y9" t="n">
-        <v>422.1209663094209</v>
+        <v>900.0695195792149</v>
       </c>
     </row>
     <row r="10">
@@ -4929,22 +4929,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>534.557758229241</v>
+        <v>741.4926772274584</v>
       </c>
       <c r="C10" t="n">
-        <v>534.557758229241</v>
+        <v>741.4926772274584</v>
       </c>
       <c r="D10" t="n">
-        <v>647.8769023542411</v>
+        <v>817.3934875136387</v>
       </c>
       <c r="E10" t="n">
-        <v>765.7058065656541</v>
+        <v>935.2223917250517</v>
       </c>
       <c r="F10" t="n">
-        <v>890.0667791575896</v>
+        <v>1059.583364316987</v>
       </c>
       <c r="G10" t="n">
-        <v>1043.473345044475</v>
+        <v>1212.989930203873</v>
       </c>
       <c r="H10" t="n">
         <v>1212.989930203873</v>
@@ -4980,25 +4980,25 @@
         <v>33.68</v>
       </c>
       <c r="S10" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T10" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="U10" t="n">
-        <v>317.4814477324597</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="V10" t="n">
-        <v>317.4814477324597</v>
+        <v>479.0525855242326</v>
       </c>
       <c r="W10" t="n">
-        <v>317.4814477324597</v>
+        <v>479.0525855242326</v>
       </c>
       <c r="X10" t="n">
-        <v>317.4814477324597</v>
+        <v>630.0833765484261</v>
       </c>
       <c r="Y10" t="n">
-        <v>422.8004205629489</v>
+        <v>741.4926772274584</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1223.616245745725</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C11" t="n">
-        <v>996.8742475204788</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D11" t="n">
-        <v>809.6629790963881</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E11" t="n">
-        <v>628.48793908945</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F11" t="n">
-        <v>446.7812434247916</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G11" t="n">
-        <v>266.2182411146742</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H11" t="n">
-        <v>81.36</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I11" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J11" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1182.375479385524</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>2089.404973955146</v>
+        <v>2081.135479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2600.253802684082</v>
+        <v>2591.984308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>3213.474122458845</v>
+        <v>3205.204627889222</v>
       </c>
       <c r="O11" t="n">
-        <v>4068</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>4068</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q11" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R11" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S11" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X11" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y11" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C12" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D12" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E12" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F12" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G12" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H12" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>73.28</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>445.7265201752989</v>
       </c>
       <c r="K12" t="n">
-        <v>643.9799167834981</v>
+        <v>883.4093362696823</v>
       </c>
       <c r="L12" t="n">
-        <v>1138.080378378698</v>
+        <v>1403.249797864883</v>
       </c>
       <c r="M12" t="n">
-        <v>1446.910920121557</v>
+        <v>1489.330339607742</v>
       </c>
       <c r="N12" t="n">
-        <v>1802.941204729126</v>
+        <v>1622.61062421531</v>
       </c>
       <c r="O12" t="n">
-        <v>2264.733656412845</v>
+        <v>1888.375790033876</v>
       </c>
       <c r="P12" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q12" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R12" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S12" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T12" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U12" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V12" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W12" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X12" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y12" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>193.6715880782802</v>
+        <v>218.7876980209074</v>
       </c>
       <c r="C13" t="n">
-        <v>193.6715880782802</v>
+        <v>196.8430044370239</v>
       </c>
       <c r="D13" t="n">
-        <v>193.6715880782802</v>
+        <v>196.8430044370239</v>
       </c>
       <c r="E13" t="n">
-        <v>193.6715880782802</v>
+        <v>166.5592621774718</v>
       </c>
       <c r="F13" t="n">
-        <v>193.6715880782802</v>
+        <v>142.9402157454092</v>
       </c>
       <c r="G13" t="n">
-        <v>193.6715880782802</v>
+        <v>148.8367816322945</v>
       </c>
       <c r="H13" t="n">
-        <v>189.862369793817</v>
+        <v>170.8433667916921</v>
       </c>
       <c r="I13" t="n">
-        <v>237.7452487298999</v>
+        <v>244.466245727775</v>
       </c>
       <c r="J13" t="n">
-        <v>425.5789893823512</v>
+        <v>458.0399863802263</v>
       </c>
       <c r="K13" t="n">
-        <v>425.5789893823512</v>
+        <v>420.1402148639202</v>
       </c>
       <c r="L13" t="n">
-        <v>425.5789893823512</v>
+        <v>420.1402148639202</v>
       </c>
       <c r="M13" t="n">
-        <v>126.9612000868462</v>
+        <v>420.1402148639202</v>
       </c>
       <c r="N13" t="n">
-        <v>126.9612000868462</v>
+        <v>420.1402148639202</v>
       </c>
       <c r="O13" t="n">
-        <v>126.9612000868462</v>
+        <v>420.1402148639202</v>
       </c>
       <c r="P13" t="n">
-        <v>81.36</v>
+        <v>185.7784643463186</v>
       </c>
       <c r="Q13" t="n">
-        <v>81.36</v>
+        <v>185.7784643463186</v>
       </c>
       <c r="R13" t="n">
-        <v>81.36</v>
+        <v>185.7784643463186</v>
       </c>
       <c r="S13" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T13" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>193.6715880782802</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X13" t="n">
-        <v>193.6715880782802</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y13" t="n">
-        <v>193.6715880782802</v>
+        <v>255.2662842199767</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1223.616245745725</v>
+        <v>1057.960488169967</v>
       </c>
       <c r="C14" t="n">
-        <v>996.8742475204788</v>
+        <v>857.4811162073474</v>
       </c>
       <c r="D14" t="n">
-        <v>809.6629790963881</v>
+        <v>696.532474045883</v>
       </c>
       <c r="E14" t="n">
-        <v>628.48793908945</v>
+        <v>541.6200603015712</v>
       </c>
       <c r="F14" t="n">
-        <v>446.7812434247916</v>
+        <v>386.175990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>266.2182411146742</v>
+        <v>231.8756148520479</v>
       </c>
       <c r="H14" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I14" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J14" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>1182.375479385524</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>2089.404973955146</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="M14" t="n">
-        <v>2600.253802684082</v>
+        <v>1685.144308114459</v>
       </c>
       <c r="N14" t="n">
-        <v>2600.253802684082</v>
+        <v>2298.364627889222</v>
       </c>
       <c r="O14" t="n">
-        <v>3553.296346706038</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="P14" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q14" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R14" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S14" t="n">
-        <v>3769.286094312508</v>
+        <v>3414.243273547741</v>
       </c>
       <c r="T14" t="n">
-        <v>3403.957223879615</v>
+        <v>3075.177029377474</v>
       </c>
       <c r="U14" t="n">
-        <v>2975.450863729503</v>
+        <v>2672.933295489988</v>
       </c>
       <c r="V14" t="n">
-        <v>2566.510435278165</v>
+        <v>2290.255493301277</v>
       </c>
       <c r="W14" t="n">
-        <v>2143.412790290219</v>
+        <v>1898.969153926582</v>
       </c>
       <c r="X14" t="n">
-        <v>1772.421039319847</v>
+        <v>1554.240029218837</v>
       </c>
       <c r="Y14" t="n">
-        <v>1483.211511357417</v>
+        <v>1291.293127519033</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C15" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D15" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E15" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F15" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G15" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H15" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I15" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J15" t="n">
-        <v>428.066520175299</v>
+        <v>445.7265201752989</v>
       </c>
       <c r="K15" t="n">
-        <v>840.0093362696824</v>
+        <v>634.9193362696823</v>
       </c>
       <c r="L15" t="n">
-        <v>1334.109797864882</v>
+        <v>906.2697978648823</v>
       </c>
       <c r="M15" t="n">
-        <v>1642.940339607742</v>
+        <v>1240.840339607741</v>
       </c>
       <c r="N15" t="n">
-        <v>1854.342732289551</v>
+        <v>1374.12062421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2316.13518397327</v>
+        <v>1861.653075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>2651.414528442776</v>
+        <v>2222.672420368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R15" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S15" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T15" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U15" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V15" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W15" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X15" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y15" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>130.5752720687223</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>130.5752720687223</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D16" t="n">
-        <v>130.5752720687223</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E16" t="n">
-        <v>130.5752720687223</v>
+        <v>261.8162317073563</v>
       </c>
       <c r="F16" t="n">
-        <v>130.5752720687223</v>
+        <v>238.1971852752938</v>
       </c>
       <c r="G16" t="n">
-        <v>130.5752720687223</v>
+        <v>244.093751162179</v>
       </c>
       <c r="H16" t="n">
-        <v>126.766053784259</v>
+        <v>266.1003363215766</v>
       </c>
       <c r="I16" t="n">
-        <v>174.6489327203419</v>
+        <v>339.7232152576595</v>
       </c>
       <c r="J16" t="n">
-        <v>362.4826733727932</v>
+        <v>553.2969559101108</v>
       </c>
       <c r="K16" t="n">
-        <v>362.4826733727932</v>
+        <v>552.9156226521192</v>
       </c>
       <c r="L16" t="n">
-        <v>362.4826733727932</v>
+        <v>552.9156226521192</v>
       </c>
       <c r="M16" t="n">
-        <v>362.4826733727932</v>
+        <v>552.9156226521192</v>
       </c>
       <c r="N16" t="n">
-        <v>362.4826733727932</v>
+        <v>552.9156226521192</v>
       </c>
       <c r="O16" t="n">
-        <v>362.4826733727932</v>
+        <v>552.9156226521192</v>
       </c>
       <c r="P16" t="n">
-        <v>362.4826733727932</v>
+        <v>552.9156226521192</v>
       </c>
       <c r="Q16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="R16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T16" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V16" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W16" t="n">
-        <v>193.6715880782802</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X16" t="n">
-        <v>193.6715880782802</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>130.5752720687223</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1223.616245745725</v>
+        <v>1057.960488169967</v>
       </c>
       <c r="C17" t="n">
-        <v>996.8742475204788</v>
+        <v>857.4811162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>809.6629790963881</v>
+        <v>696.532474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>628.48793908945</v>
+        <v>541.6200603015712</v>
       </c>
       <c r="F17" t="n">
-        <v>446.7812434247916</v>
+        <v>386.175990899539</v>
       </c>
       <c r="G17" t="n">
-        <v>266.2182411146742</v>
+        <v>231.8756148520479</v>
       </c>
       <c r="H17" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I17" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J17" t="n">
-        <v>81.36</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>791.0663663478683</v>
+        <v>900.8720762183972</v>
       </c>
       <c r="L17" t="n">
-        <v>1698.095860917491</v>
+        <v>1807.712076218397</v>
       </c>
       <c r="M17" t="n">
-        <v>2208.944689646426</v>
+        <v>2318.560904947332</v>
       </c>
       <c r="N17" t="n">
-        <v>2822.165009421189</v>
+        <v>2318.560904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>2822.165009421189</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q17" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R17" t="n">
-        <v>4036.311321832915</v>
+        <v>3664</v>
       </c>
       <c r="S17" t="n">
-        <v>3763.737414961882</v>
+        <v>3414.243273547741</v>
       </c>
       <c r="T17" t="n">
-        <v>3398.408544528989</v>
+        <v>3075.177029377474</v>
       </c>
       <c r="U17" t="n">
-        <v>2969.902184378877</v>
+        <v>2672.933295489988</v>
       </c>
       <c r="V17" t="n">
-        <v>2560.961755927539</v>
+        <v>2290.255493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>2143.412790290219</v>
+        <v>1898.969153926582</v>
       </c>
       <c r="X17" t="n">
-        <v>1772.421039319847</v>
+        <v>1554.240029218837</v>
       </c>
       <c r="Y17" t="n">
-        <v>1483.211511357417</v>
+        <v>1291.293127519033</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C18" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D18" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E18" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F18" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G18" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H18" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I18" t="n">
-        <v>81.36</v>
+        <v>106.814877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>428.066520175299</v>
+        <v>230.7713981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>840.0093362696824</v>
+        <v>419.9642142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>1334.109797864882</v>
+        <v>691.3146758324474</v>
       </c>
       <c r="M18" t="n">
-        <v>1642.940339607742</v>
+        <v>1025.885217575307</v>
       </c>
       <c r="N18" t="n">
-        <v>1802.941204729126</v>
+        <v>1323.701810789732</v>
       </c>
       <c r="O18" t="n">
-        <v>2264.733656412845</v>
+        <v>1811.23426247345</v>
       </c>
       <c r="P18" t="n">
-        <v>2600.013000882351</v>
+        <v>2172.253606942957</v>
       </c>
       <c r="Q18" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R18" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S18" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T18" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U18" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V18" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W18" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X18" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y18" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>193.6715880782802</v>
+        <v>255.6213877678391</v>
       </c>
       <c r="C19" t="n">
-        <v>193.6715880782802</v>
+        <v>233.6766941839555</v>
       </c>
       <c r="D19" t="n">
-        <v>193.6715880782802</v>
+        <v>233.6766941839555</v>
       </c>
       <c r="E19" t="n">
-        <v>193.6715880782802</v>
+        <v>233.6766941839555</v>
       </c>
       <c r="F19" t="n">
-        <v>193.6715880782802</v>
+        <v>210.057647751893</v>
       </c>
       <c r="G19" t="n">
-        <v>193.6715880782802</v>
+        <v>215.9542136387782</v>
       </c>
       <c r="H19" t="n">
-        <v>189.862369793817</v>
+        <v>237.9607987981758</v>
       </c>
       <c r="I19" t="n">
-        <v>237.7452487298999</v>
+        <v>311.5836777342587</v>
       </c>
       <c r="J19" t="n">
-        <v>425.5789893823512</v>
+        <v>525.15741838671</v>
       </c>
       <c r="K19" t="n">
-        <v>425.5789893823512</v>
+        <v>525.15741838671</v>
       </c>
       <c r="L19" t="n">
-        <v>379.977789295505</v>
+        <v>525.15741838671</v>
       </c>
       <c r="M19" t="n">
-        <v>81.36</v>
+        <v>514.136461947755</v>
       </c>
       <c r="N19" t="n">
-        <v>81.36</v>
+        <v>514.136461947755</v>
       </c>
       <c r="O19" t="n">
-        <v>81.36</v>
+        <v>514.136461947755</v>
       </c>
       <c r="P19" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="R19" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S19" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T19" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>193.6715880782802</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>193.6715880782802</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>193.6715880782802</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1229.164925096351</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C20" t="n">
-        <v>1002.422926871105</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D20" t="n">
-        <v>815.2116584470142</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E20" t="n">
-        <v>634.0366184400762</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F20" t="n">
-        <v>452.3299227754177</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G20" t="n">
-        <v>271.7669204653003</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H20" t="n">
-        <v>86.90867935062613</v>
+        <v>73.28</v>
       </c>
       <c r="I20" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J20" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1182.375479385524</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>2089.404973955146</v>
+        <v>2081.135479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>2600.253802684082</v>
+        <v>2591.984308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>3213.474122458845</v>
+        <v>3205.204627889222</v>
       </c>
       <c r="O20" t="n">
-        <v>3629.400904947332</v>
+        <v>3205.204627889222</v>
       </c>
       <c r="P20" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q20" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R20" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S20" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X20" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y20" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C21" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D21" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E21" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F21" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G21" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H21" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I21" t="n">
-        <v>89.15487796756496</v>
+        <v>73.28</v>
       </c>
       <c r="J21" t="n">
-        <v>435.8613981428639</v>
+        <v>445.7265201752989</v>
       </c>
       <c r="K21" t="n">
-        <v>643.9799167834981</v>
+        <v>634.9193362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>1138.080378378698</v>
+        <v>1154.759797864882</v>
       </c>
       <c r="M21" t="n">
-        <v>1446.910920121557</v>
+        <v>1489.330339607742</v>
       </c>
       <c r="N21" t="n">
-        <v>1802.941204729126</v>
+        <v>1871.10062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>2264.733656412845</v>
+        <v>2136.865790033876</v>
       </c>
       <c r="P21" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q21" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R21" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S21" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T21" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U21" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V21" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W21" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X21" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y21" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="F22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="G22" t="n">
-        <v>195.0582646830375</v>
+        <v>297.9965398537936</v>
       </c>
       <c r="H22" t="n">
-        <v>195.0582646830375</v>
+        <v>320.0031250131912</v>
       </c>
       <c r="I22" t="n">
-        <v>242.9411436191204</v>
+        <v>393.6260039492741</v>
       </c>
       <c r="J22" t="n">
-        <v>430.7748842715717</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="K22" t="n">
-        <v>430.7748842715717</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="L22" t="n">
-        <v>430.7748842715717</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="M22" t="n">
-        <v>430.7748842715717</v>
+        <v>334.8445815688468</v>
       </c>
       <c r="N22" t="n">
-        <v>430.7748842715717</v>
+        <v>334.8445815688468</v>
       </c>
       <c r="O22" t="n">
-        <v>430.7748842715717</v>
+        <v>73.28</v>
       </c>
       <c r="P22" t="n">
-        <v>430.7748842715717</v>
+        <v>73.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="R22" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S22" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T22" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U22" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V22" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>195.0582646830375</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>195.0582646830375</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1229.164925096351</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C23" t="n">
-        <v>1002.422926871105</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D23" t="n">
-        <v>815.2116584470142</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E23" t="n">
-        <v>634.0366184400762</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F23" t="n">
-        <v>452.3299227754177</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G23" t="n">
-        <v>271.7669204653003</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H23" t="n">
-        <v>86.90867935062613</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I23" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J23" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1182.375479385524</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1552.289212421678</v>
+        <v>2081.135479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>2063.138041150613</v>
+        <v>2591.984308114459</v>
       </c>
       <c r="N23" t="n">
-        <v>2676.358360925376</v>
+        <v>3205.204627889222</v>
       </c>
       <c r="O23" t="n">
-        <v>3629.400904947332</v>
+        <v>3205.204627889222</v>
       </c>
       <c r="P23" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q23" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R23" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S23" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X23" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y23" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C24" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D24" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E24" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F24" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G24" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H24" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I24" t="n">
-        <v>89.15487796756496</v>
+        <v>100.0027141348468</v>
       </c>
       <c r="J24" t="n">
-        <v>435.8613981428639</v>
+        <v>472.4492343101457</v>
       </c>
       <c r="K24" t="n">
-        <v>847.8042142372474</v>
+        <v>661.6420504045291</v>
       </c>
       <c r="L24" t="n">
-        <v>1138.080378378698</v>
+        <v>1181.482511999729</v>
       </c>
       <c r="M24" t="n">
-        <v>1446.910920121557</v>
+        <v>1267.563053742588</v>
       </c>
       <c r="N24" t="n">
-        <v>1802.941204729126</v>
+        <v>1649.333338350157</v>
       </c>
       <c r="O24" t="n">
-        <v>2264.733656412845</v>
+        <v>2136.865790033876</v>
       </c>
       <c r="P24" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q24" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R24" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S24" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T24" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U24" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V24" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W24" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X24" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y24" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>196.1985859847637</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C25" t="n">
-        <v>196.1985859847637</v>
+        <v>270.1552803830249</v>
       </c>
       <c r="D25" t="n">
-        <v>135.0508909791521</v>
+        <v>270.1552803830249</v>
       </c>
       <c r="E25" t="n">
-        <v>135.0508909791521</v>
+        <v>239.8715381234728</v>
       </c>
       <c r="F25" t="n">
-        <v>85.16921828446326</v>
+        <v>238.5864192451336</v>
       </c>
       <c r="G25" t="n">
-        <v>85.16921828446326</v>
+        <v>244.4829851320188</v>
       </c>
       <c r="H25" t="n">
-        <v>81.36</v>
+        <v>266.4895702914164</v>
       </c>
       <c r="I25" t="n">
-        <v>129.2428789360829</v>
+        <v>340.1124492274993</v>
       </c>
       <c r="J25" t="n">
-        <v>317.0766195885342</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="K25" t="n">
-        <v>317.0766195885342</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="L25" t="n">
-        <v>317.0766195885342</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="M25" t="n">
-        <v>146.9833139160415</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="N25" t="n">
-        <v>146.9833139160415</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="O25" t="n">
-        <v>146.9833139160415</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="P25" t="n">
-        <v>146.9833139160415</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="Q25" t="n">
-        <v>146.9833139160415</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="R25" t="n">
-        <v>146.9833139160415</v>
+        <v>73.28</v>
       </c>
       <c r="S25" t="n">
-        <v>146.9833139160415</v>
+        <v>73.28</v>
       </c>
       <c r="T25" t="n">
-        <v>161.8089930748463</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>235.110185713133</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>260.6815785990789</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>259.2949019943217</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>259.2949019943217</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>196.1985859847637</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="26">
@@ -6220,19 +6220,19 @@
         <v>81.36</v>
       </c>
       <c r="K26" t="n">
-        <v>81.36</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L26" t="n">
-        <v>988.3894945696223</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M26" t="n">
-        <v>1499.238323298558</v>
+        <v>2208.944689646426</v>
       </c>
       <c r="N26" t="n">
-        <v>2112.458643073321</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="O26" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>3629.400904947332</v>
@@ -6305,13 +6305,13 @@
         <v>1334.109797864882</v>
       </c>
       <c r="M27" t="n">
-        <v>1446.910920121557</v>
+        <v>1642.940339607742</v>
       </c>
       <c r="N27" t="n">
-        <v>1802.941204729126</v>
+        <v>1998.97062421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2264.733656412845</v>
+        <v>2460.763075899029</v>
       </c>
       <c r="P27" t="n">
         <v>2600.013000882351</v>
@@ -6363,37 +6363,37 @@
         <v>195.0582646830375</v>
       </c>
       <c r="F28" t="n">
-        <v>195.0582646830375</v>
+        <v>145.1765919883486</v>
       </c>
       <c r="G28" t="n">
-        <v>195.0582646830375</v>
+        <v>145.1765919883486</v>
       </c>
       <c r="H28" t="n">
-        <v>191.2490463985742</v>
+        <v>145.1765919883486</v>
       </c>
       <c r="I28" t="n">
-        <v>239.1319253346571</v>
+        <v>193.0594709244315</v>
       </c>
       <c r="J28" t="n">
-        <v>426.9656659871084</v>
+        <v>380.8932115768829</v>
       </c>
       <c r="K28" t="n">
-        <v>426.9656659871084</v>
+        <v>380.8932115768829</v>
       </c>
       <c r="L28" t="n">
-        <v>426.9656659871084</v>
+        <v>380.8932115768829</v>
       </c>
       <c r="M28" t="n">
-        <v>426.9656659871084</v>
+        <v>82.27542228137793</v>
       </c>
       <c r="N28" t="n">
-        <v>426.9656659871084</v>
+        <v>81.36</v>
       </c>
       <c r="O28" t="n">
-        <v>426.9656659871084</v>
+        <v>81.36</v>
       </c>
       <c r="P28" t="n">
-        <v>426.9656659871084</v>
+        <v>81.36</v>
       </c>
       <c r="Q28" t="n">
         <v>81.36</v>
@@ -6430,46 +6430,46 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C29" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D29" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F29" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H29" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I29" t="n">
         <v>81.36</v>
       </c>
       <c r="J29" t="n">
-        <v>446.402180233122</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>1156.10854658099</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="L29" t="n">
-        <v>2063.138041150613</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M29" t="n">
-        <v>2063.138041150613</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N29" t="n">
-        <v>2676.358360925376</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O29" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P29" t="n">
         <v>3629.400904947332</v>
@@ -6484,22 +6484,22 @@
         <v>3769.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U29" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V29" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W29" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X29" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y29" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="30">
@@ -6530,25 +6530,25 @@
         <v>81.36</v>
       </c>
       <c r="I30" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J30" t="n">
-        <v>435.8613981428639</v>
+        <v>428.066520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>847.8042142372474</v>
+        <v>840.0093362696824</v>
       </c>
       <c r="L30" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M30" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N30" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P30" t="n">
         <v>2600.013000882351</v>
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>193.6715880782802</v>
+        <v>132.3170522213418</v>
       </c>
       <c r="C31" t="n">
-        <v>193.6715880782802</v>
+        <v>132.3170522213418</v>
       </c>
       <c r="D31" t="n">
-        <v>132.5238930726686</v>
+        <v>132.3170522213418</v>
       </c>
       <c r="E31" t="n">
-        <v>132.5238930726686</v>
+        <v>81.36</v>
       </c>
       <c r="F31" t="n">
-        <v>132.5238930726686</v>
+        <v>81.36</v>
       </c>
       <c r="G31" t="n">
-        <v>132.5238930726686</v>
+        <v>81.36</v>
       </c>
       <c r="H31" t="n">
-        <v>128.7146747882053</v>
+        <v>81.36</v>
       </c>
       <c r="I31" t="n">
-        <v>176.5975537242882</v>
+        <v>129.2428789360829</v>
       </c>
       <c r="J31" t="n">
-        <v>364.4312943767396</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="K31" t="n">
-        <v>364.4312943767396</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="L31" t="n">
-        <v>364.4312943767396</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="M31" t="n">
-        <v>364.4312943767396</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="N31" t="n">
-        <v>364.4312943767396</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="O31" t="n">
-        <v>81.36</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="P31" t="n">
-        <v>81.36</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="Q31" t="n">
-        <v>81.36</v>
+        <v>317.0766195885342</v>
       </c>
       <c r="R31" t="n">
         <v>81.36</v>
@@ -6651,13 +6651,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="X31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="Y31" t="n">
-        <v>193.6715880782802</v>
+        <v>195.0582646830375</v>
       </c>
     </row>
     <row r="32">
@@ -6691,49 +6691,49 @@
         <v>81.36</v>
       </c>
       <c r="J32" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K32" t="n">
-        <v>1182.375479385524</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L32" t="n">
-        <v>1303.921568289334</v>
+        <v>1698.095860917491</v>
       </c>
       <c r="M32" t="n">
-        <v>1814.770397018269</v>
+        <v>2208.944689646426</v>
       </c>
       <c r="N32" t="n">
-        <v>1814.770397018269</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="O32" t="n">
-        <v>2767.812941040225</v>
+        <v>2822.165009421189</v>
       </c>
       <c r="P32" t="n">
-        <v>3629.400904947332</v>
+        <v>3683.752973328296</v>
       </c>
       <c r="Q32" t="n">
         <v>4068</v>
       </c>
       <c r="R32" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S32" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T32" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U32" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V32" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W32" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X32" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y32" t="n">
         <v>1483.211511357417</v>
@@ -6782,10 +6782,10 @@
         <v>1650.735217575307</v>
       </c>
       <c r="N33" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P33" t="n">
         <v>2600.013000882351</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H34" t="n">
-        <v>195.0582646830375</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I34" t="n">
-        <v>242.9411436191204</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q34" t="n">
-        <v>430.7748842715717</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6888,13 +6888,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="35">
@@ -6937,16 +6937,16 @@
         <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="N35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,13 +6983,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E36" t="n">
         <v>387.7869114524009</v>
@@ -7046,13 +7046,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>554.3632764052976</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="37">
@@ -7062,31 +7062,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H37" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J37" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K37" t="n">
         <v>1921.561060958496</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7168,22 +7168,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L38" t="n">
-        <v>989.4391130376558</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M38" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="N38" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="O38" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="P38" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
         <v>44.72</v>
@@ -7283,13 +7283,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J40" t="n">
         <v>1860.696627021627</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7387,16 +7387,16 @@
         <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
@@ -7414,13 +7414,13 @@
         <v>1662.388828728935</v>
       </c>
       <c r="N41" t="n">
-        <v>2215.798828728935</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O41" t="n">
-        <v>2236</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="P41" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G42" t="n">
         <v>44.72</v>
@@ -7511,22 +7511,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7590,7 +7590,7 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
         <v>372.6360891248843</v>
@@ -7639,25 +7639,25 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M44" t="n">
-        <v>598.13</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1151.54</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>1704.95</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7694,13 +7694,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
-        <v>390.8534315372855</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D45" t="n">
-        <v>390.8534315372855</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E45" t="n">
         <v>44.72</v>
@@ -7751,19 +7751,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907175</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="46">
@@ -7967,25 +7967,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>948.2520266322164</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>898.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>491.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>421.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>593.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,13 +8204,13 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>421</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="L5" t="n">
-        <v>421.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>948.2520266322163</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>898.2489580698352</v>
@@ -8222,7 +8222,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>593.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8447,16 +8447,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N8" t="n">
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>491.2478695740924</v>
+        <v>78.97603822292498</v>
       </c>
       <c r="P8" t="n">
-        <v>9.015228689513952</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
         <v>593.8226843274854</v>
@@ -8681,7 +8681,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,13 +8690,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>933.4053216358654</v>
+        <v>90.64814943076958</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,19 +8918,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>1032.917105959907</v>
+        <v>136.3572767973281</v>
       </c>
       <c r="P14" t="n">
-        <v>77.16035119350404</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>440.6898617987288</v>
       </c>
       <c r="L17" t="n">
-        <v>916.1914086561842</v>
+        <v>916</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>815.6768535014329</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9392,7 +9392,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>916.1914086561842</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,10 +9401,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>490.3759326937771</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>20.68733989735854</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9629,7 +9629,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>373.6502353900541</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,10 +9638,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>20.68733989735854</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9863,7 +9863,7 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
         <v>916.1914086561842</v>
@@ -9875,10 +9875,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>732.2219079245011</v>
+        <v>885.6376630348439</v>
       </c>
       <c r="P26" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,16 +10097,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>403.772481228042</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
@@ -10115,7 +10115,7 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>122.773827175565</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
         <v>870.5779326741233</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>560.9509940968831</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,10 +10580,10 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>801.3851497733039</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
@@ -10592,7 +10592,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
@@ -10829,7 +10829,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>356.9661774925453</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11057,16 +11057,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>90.65309308021877</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>136.6628946047192</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>801.385149773304</v>
       </c>
       <c r="N44" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>536.7012014548231</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23381,22 +23381,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -23408,31 +23408,31 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>417.3027092422997</v>
+        <v>204.4297643158519</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23447,10 +23447,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -23618,22 +23618,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,31 +23645,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>63.52077380114304</v>
+        <v>37.14325387573133</v>
       </c>
       <c r="L16" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>295.6316114025499</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>222.5278197865327</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23684,10 +23684,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23855,22 +23855,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F19" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -23882,31 +23882,31 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L19" t="n">
-        <v>153.4024400718014</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>258.7208645279845</v>
       </c>
       <c r="N19" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>462.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>500.839266425598</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23921,10 +23921,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -24092,25 +24092,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C22" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D22" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F22" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G22" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -24119,31 +24119,31 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L22" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>415.445564079015</v>
+        <v>130.4966283258567</v>
       </c>
       <c r="P22" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>154.918530996742</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24155,13 +24155,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -24329,22 +24329,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C25" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>22.11058827818606</v>
       </c>
       <c r="G25" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -24356,31 +24356,31 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L25" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>127.239238786782</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>500.839266425598</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>501.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24395,10 +24395,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -24578,13 +24578,13 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24599,10 +24599,10 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>345.2788072131208</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24611,7 +24611,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>158.6896570983607</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
@@ -24803,16 +24803,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>55.98090483695654</v>
+        <v>5.533423137828116</v>
       </c>
       <c r="F31" t="n">
         <v>49.38285596774193</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24842,7 +24842,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>135.2049826460428</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
         <v>462.4478973282775</v>
@@ -24851,7 +24851,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>501.6021279811511</v>
+        <v>268.2426745885022</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25058,7 +25058,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H34" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25088,7 +25088,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>155.6813925522951</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>22.44364543010755</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4182363.690807104</v>
+        <v>4189870.422721177</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5162711.880353261</v>
+        <v>5182500.379332922</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6143060.069899414</v>
+        <v>6175130.335944665</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7123408.259445566</v>
+        <v>7167760.292556404</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8103756.448991718</v>
+        <v>8160390.249168144</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9084104.638537871</v>
+        <v>9145513.473865811</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10064452.82808402</v>
+        <v>10125861.66341196</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11044801.01763017</v>
+        <v>11106209.85295811</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12062133.9462076</v>
+        <v>12123542.78153554</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13101120.004482</v>
+        <v>13162528.83980994</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14140106.0627564</v>
+        <v>14201514.89808434</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15179092.1210308</v>
+        <v>15240500.95635873</v>
       </c>
     </row>
   </sheetData>
@@ -26272,25 +26272,25 @@
         <v>1164923.76230765</v>
       </c>
       <c r="C2" t="n">
-        <v>1164923.76230765</v>
+        <v>1164923.762307651</v>
       </c>
       <c r="D2" t="n">
         <v>1164923.76230765</v>
       </c>
       <c r="E2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="F2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.73923135</v>
       </c>
       <c r="G2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="H2" t="n">
-        <v>1099178.273127509</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="I2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="J2" t="n">
         <v>1099178.273127508</v>
@@ -26308,7 +26308,7 @@
         <v>1164923.762307649</v>
       </c>
       <c r="O2" t="n">
-        <v>1164923.762307649</v>
+        <v>1164923.76230765</v>
       </c>
       <c r="P2" t="n">
         <v>1164923.76230765</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>389792</v>
+        <v>375040</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>328192</v>
+        <v>363744</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>148576</v>
+        <v>113024</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359546</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743711</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>468964.8457662077</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482318</v>
+        <v>467405.5293950558</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>465844.0612258157</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>464280.4258278603</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>462714.6075695099</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696402</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464519</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26434,19 +26434,19 @@
         <v>59224.39999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="F5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="G5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="H5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="I5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="J5" t="n">
         <v>80749.125</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>391152.4030651407</v>
+        <v>389589.7899716953</v>
       </c>
       <c r="C6" t="n">
-        <v>541376.9188286854</v>
+        <v>539814.3057352408</v>
       </c>
       <c r="D6" t="n">
-        <v>543412.1918267241</v>
+        <v>541849.5787332793</v>
       </c>
       <c r="E6" t="n">
-        <v>182784.4586156467</v>
+        <v>192149.7744651418</v>
       </c>
       <c r="F6" t="n">
-        <v>574030.0093792765</v>
+        <v>568749.0908362939</v>
       </c>
       <c r="G6" t="n">
-        <v>575485.5659884247</v>
+        <v>570310.5590055336</v>
       </c>
       <c r="H6" t="n">
-        <v>576943.1428270871</v>
+        <v>571874.1944034892</v>
       </c>
       <c r="I6" t="n">
-        <v>578402.7544666729</v>
+        <v>573440.0126618396</v>
       </c>
       <c r="J6" t="n">
-        <v>251672.4156695653</v>
+        <v>213783.7077578679</v>
       </c>
       <c r="K6" t="n">
-        <v>581328.1413927537</v>
+        <v>578991.4334810562</v>
       </c>
       <c r="L6" t="n">
-        <v>582793.9467915709</v>
+        <v>580457.2388798737</v>
       </c>
       <c r="M6" t="n">
-        <v>425461.6877655491</v>
+        <v>459271.837952442</v>
       </c>
       <c r="N6" t="n">
-        <v>576002.5848004022</v>
+        <v>574260.7349872943</v>
       </c>
       <c r="O6" t="n">
-        <v>397970.3240581403</v>
+        <v>396228.4742450329</v>
       </c>
       <c r="P6" t="n">
-        <v>579940.9269091507</v>
+        <v>578199.0770960434</v>
       </c>
     </row>
   </sheetData>
@@ -26764,19 +26764,19 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J2" t="n">
         <v>225</v>
@@ -26868,19 +26868,19 @@
         <v>421</v>
       </c>
       <c r="E4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="F4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="G4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="H4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="I4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="J4" t="n">
         <v>1017</v>
@@ -26981,13 +26981,13 @@
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27027,7 +27027,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -27039,7 +27039,7 @@
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>421</v>
+        <v>522</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27213,7 +27213,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27521,10 +27521,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>57.41713069510376</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>98.42839661193709</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27606,16 +27606,16 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
       </c>
-      <c r="I4" t="n">
-        <v>244.6319613619525</v>
-      </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>107.4085132638902</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27645,22 +27645,22 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U4" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V4" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W4" t="n">
         <v>400</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>400</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>400</v>
-      </c>
-      <c r="W4" t="n">
-        <v>226.3728098387097</v>
-      </c>
-      <c r="X4" t="n">
-        <v>247.4436454301076</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,7 +27676,7 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="E5" t="n">
         <v>400</v>
@@ -27736,7 +27736,7 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>400</v>
+        <v>381.6661682972701</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27758,13 +27758,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>158.62369561122</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,7 +27803,7 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>63.29132760475932</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27828,22 +27828,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>316.825164285699</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>243.4589301351605</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X7" t="n">
         <v>400</v>
-      </c>
-      <c r="X7" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27916,7 +27916,7 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>381.6661682972702</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>232.5447671255646</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>52.66876113986626</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28004,10 +28004,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>326.8309322629039</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,13 +28065,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>362.2037031931113</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
@@ -28083,7 +28083,7 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
@@ -28125,16 +28125,16 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>393.8481536883403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28144,28 +28144,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>219.5068074428801</v>
+        <v>251</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I11" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,28 +28192,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -28223,76 +28223,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K12" t="n">
-        <v>19.11687125883913</v>
+        <v>251</v>
       </c>
       <c r="L12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>225</v>
+        <v>26.99264054024931</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q12" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13">
@@ -28302,76 +28302,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14">
@@ -28381,25 +28381,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I14" t="n">
         <v>150.0811596826846</v>
@@ -28429,28 +28429,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>225</v>
+        <v>247.589008614586</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W14" t="n">
-        <v>219.5068074428802</v>
+        <v>251</v>
       </c>
       <c r="X14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15">
@@ -28460,76 +28460,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K15" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>78.9112202770111</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q15" t="n">
-        <v>173.0792650904796</v>
+        <v>200.0719056307292</v>
       </c>
       <c r="R15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
@@ -28539,76 +28539,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17">
@@ -28618,25 +28618,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I17" t="n">
         <v>150.0811596826846</v>
@@ -28666,28 +28666,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>219.5068074428802</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>225</v>
+        <v>247.589008614586</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18">
@@ -28697,76 +28697,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>251</v>
       </c>
       <c r="J18" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N18" t="n">
-        <v>26.99048536749072</v>
+        <v>166.1982915220775</v>
       </c>
       <c r="O18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19">
@@ -28776,76 +28776,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20">
@@ -28855,28 +28855,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H20" t="n">
-        <v>225</v>
+        <v>247.589008614586</v>
       </c>
       <c r="I20" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,28 +28903,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21">
@@ -28934,76 +28934,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I21" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K21" t="n">
-        <v>19.11687125883913</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O21" t="n">
-        <v>225</v>
+        <v>26.99264054024954</v>
       </c>
       <c r="P21" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22">
@@ -29013,76 +29013,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23">
@@ -29092,28 +29092,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I23" t="n">
-        <v>144.5879671255647</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,28 +29140,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24">
@@ -29171,76 +29171,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I24" t="n">
-        <v>225</v>
+        <v>244.1190264315978</v>
       </c>
       <c r="J24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K24" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>19.11687125883913</v>
+        <v>251</v>
       </c>
       <c r="M24" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P24" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25">
@@ -29250,76 +29250,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26">
@@ -29441,7 +29441,7 @@
         <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>26.99048536749062</v>
+        <v>225</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>26.99048536749045</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29587,7 +29587,7 @@
         <v>225</v>
       </c>
       <c r="I29" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29620,7 +29620,7 @@
         <v>225</v>
       </c>
       <c r="T29" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="U29" t="n">
         <v>225</v>
@@ -29666,7 +29666,7 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
         <v>225</v>
@@ -29675,7 +29675,7 @@
         <v>225</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>26.99048536749063</v>
       </c>
       <c r="M30" t="n">
         <v>225</v>
@@ -29687,7 +29687,7 @@
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S32" t="n">
         <v>225</v>
@@ -29872,7 +29872,7 @@
         <v>225</v>
       </c>
       <c r="Y32" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
     </row>
     <row r="33">
@@ -29918,13 +29918,13 @@
         <v>225</v>
       </c>
       <c r="N33" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O33" t="n">
         <v>225</v>
       </c>
       <c r="P33" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q33" t="n">
         <v>225</v>
@@ -30128,7 +30128,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -30182,7 +30182,7 @@
         <v>350</v>
       </c>
       <c r="W36" t="n">
-        <v>350</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="X36" t="n">
         <v>350</v>
@@ -30225,7 +30225,7 @@
         <v>350</v>
       </c>
       <c r="K37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
@@ -30365,7 +30365,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30374,7 +30374,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>262.1624218828912</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30419,7 +30419,7 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="X39" t="n">
         <v>350</v>
@@ -30459,7 +30459,7 @@
         <v>350</v>
       </c>
       <c r="J40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30523,7 +30523,7 @@
         <v>350</v>
       </c>
       <c r="E41" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="F41" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30602,13 +30602,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>255.7338705714974</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
@@ -30647,10 +30647,10 @@
         <v>350</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U42" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V42" t="n">
         <v>350</v>
@@ -30726,10 +30726,10 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
+        <v>350</v>
+      </c>
+      <c r="U43" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U43" t="n">
-        <v>350</v>
       </c>
       <c r="V43" t="n">
         <v>350</v>
@@ -30833,13 +30833,13 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>279.9943346964702</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
@@ -30887,7 +30887,7 @@
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>350</v>
@@ -34746,25 +34746,25 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>403.989898989899</v>
+        <v>421</v>
       </c>
       <c r="N2" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>421</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="Q2" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,16 +34892,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>67.99850574183429</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>72.13956442798246</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,13 +34983,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>403.9898989898991</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>421</v>
-      </c>
-      <c r="L5" t="n">
-        <v>421.0000000000001</v>
-      </c>
-      <c r="M5" t="n">
-        <v>403.9898989898989</v>
       </c>
       <c r="N5" t="n">
         <v>421</v>
@@ -35001,7 +35001,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,22 +35114,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>35.84425944874249</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35138,10 +35138,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>92.50053886070258</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35226,16 +35226,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="N8" t="n">
         <v>421</v>
       </c>
       <c r="O8" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="P8" t="n">
-        <v>8.728168648832536</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>421</v>
@@ -35351,13 +35351,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>76.66748513755577</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
@@ -35369,7 +35369,7 @@
         <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>106.3828008388779</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,13 +35469,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>863.157452061773</v>
+        <v>20.40027985667713</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,31 +35530,31 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>210.2207258996305</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>499.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N12" t="n">
-        <v>359.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>466.4570219027464</v>
+        <v>268.4496624429957</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35603,16 +35603,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I13" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J13" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -35642,19 +35642,19 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U13" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V13" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -35694,22 +35694,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>962.6692363858147</v>
+        <v>66.10940722323564</v>
       </c>
       <c r="P14" t="n">
-        <v>76.87329115282263</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35770,28 +35770,28 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>416.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>499.091375348687</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>213.5377703856659</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>466.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>338.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>26.99264054024963</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35840,16 +35840,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I16" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J16" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -35879,19 +35879,19 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U16" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V16" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230993</v>
+        <v>440.6898617987288</v>
       </c>
       <c r="L17" t="n">
-        <v>916.1914086561842</v>
+        <v>916</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="P17" t="n">
-        <v>815.3897934607513</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36004,31 +36004,31 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>350.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>416.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>499.091375348687</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>161.6170354761456</v>
+        <v>300.8248416307323</v>
       </c>
       <c r="O18" t="n">
-        <v>466.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>338.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>51.92073490952041</v>
+        <v>77.92073490952041</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36077,16 +36077,16 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I19" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J19" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -36116,19 +36116,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U19" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V19" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -36168,10 +36168,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>916.1914086561842</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,10 +36180,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>420.1280631196846</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>20.40027985667713</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36241,31 +36241,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>210.2207258996305</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>499.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M21" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>359.6265501086548</v>
+        <v>385.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>466.4570219027464</v>
+        <v>268.4496624429959</v>
       </c>
       <c r="P21" t="n">
-        <v>338.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36314,16 +36314,16 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I22" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J22" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -36353,19 +36353,19 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U22" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V22" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -36405,10 +36405,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L23" t="n">
-        <v>373.6502353900541</v>
+        <v>915.9999999999998</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,10 +36417,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>20.40027985667713</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36478,31 +36478,31 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.873614108651466</v>
+        <v>26.99264054024926</v>
       </c>
       <c r="J24" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>416.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>293.2082466075261</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M24" t="n">
-        <v>311.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>359.6265501086548</v>
+        <v>385.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>466.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>338.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36551,16 +36551,16 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I25" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J25" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -36590,19 +36590,19 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U25" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -36642,7 +36642,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L26" t="n">
         <v>916.1914086561842</v>
@@ -36654,10 +36654,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>661.9740383504087</v>
+        <v>815.3897934607513</v>
       </c>
       <c r="P26" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36727,7 +36727,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>113.9405275319949</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>140.6564898821437</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36876,16 +36876,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>368.7294749829516</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
@@ -36894,7 +36894,7 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>350.2086062376757</v>
@@ -36961,7 +36961,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>499.091375348687</v>
+        <v>301.0818607161776</v>
       </c>
       <c r="M30" t="n">
         <v>311.9500421645043</v>
@@ -36973,7 +36973,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L32" t="n">
-        <v>122.773827175565</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>870.2908726334418</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>388.1283097693977</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37204,13 +37204,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N33" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O33" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>51.92073490952041</v>
@@ -37359,10 +37359,10 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>257.1230221309866</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37511,7 +37511,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K37" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37590,7 +37590,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
@@ -37608,7 +37608,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
         <v>61.47922619885696</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37836,16 +37836,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596762</v>
       </c>
       <c r="V43" t="n">
         <v>150.8296897837838</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -38070,19 +38070,19 @@
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>257.1230221309867</v>
       </c>
       <c r="N44" t="n">
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>536.4141414141416</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
